--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleBackInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleBackInfo.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>样品退回单号</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>物流单号</t>
+  </si>
+  <si>
+    <t>{.logisticsNo}</t>
   </si>
 </sst>
 </file>
@@ -1101,25 +1107,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
     <col min="2" max="2" width="22.25" customWidth="1"/>
     <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="24.625" customWidth="1"/>
-    <col min="7" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="15.75" customWidth="1"/>
-    <col min="10" max="10" width="18.75" customWidth="1"/>
-    <col min="11" max="11" width="17.625" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="8.875" customWidth="1"/>
+    <col min="5" max="5" width="17.8166666666667" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="24.625" customWidth="1"/>
+    <col min="8" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="18.75" customWidth="1"/>
+    <col min="12" max="12" width="17.625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="19.25" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:14">
+    <row r="1" customFormat="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,37 +1140,40 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1177,33 +1187,36 @@
         <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
